--- a/diseases/d122/2010-2014.xlsx
+++ b/diseases/d122/2010-2014.xlsx
@@ -33356,6 +33356,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45004,6 +45009,11 @@
       <c r="S226" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO226" t="inlineStr">
